--- a/Content/calculetion.xlsx
+++ b/Content/calculetion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riprakas\OneDrive - Capgemini\Ridham\New folder\J.-Varshit\Content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/ridham_prakash-jasani_capgemini_com/Documents/Ridham/New folder/J.-Varshit/Content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B74C40C-F7C2-45DA-9F0A-0FE86FB735C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{1B74C40C-F7C2-45DA-9F0A-0FE86FB735C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661A339C-3C41-4B83-AE39-AC5BDAFC6E31}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="price" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>usd rate</t>
   </si>
@@ -183,9 +183,6 @@
     <t>brilliaunt round</t>
   </si>
   <si>
-    <t>very good</t>
-  </si>
-  <si>
     <t>GH</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
     <t>market view</t>
   </si>
   <si>
-    <t>good</t>
-  </si>
-  <si>
     <t>HI</t>
   </si>
   <si>
@@ -247,6 +241,36 @@
   </si>
   <si>
     <t>weight</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>light brown</t>
+  </si>
+  <si>
+    <t>light yellow</t>
+  </si>
+  <si>
+    <t>lb</t>
+  </si>
+  <si>
+    <t>lc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g start h,I,j,k </t>
+  </si>
+  <si>
+    <t>light yellow (lc)</t>
+  </si>
+  <si>
+    <t>light brown (lb)</t>
+  </si>
+  <si>
+    <t>very good / good</t>
+  </si>
+  <si>
+    <t>size</t>
   </si>
 </sst>
 </file>
@@ -803,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="10.26953125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.26953125" style="1"/>
@@ -812,10 +836,12 @@
     <col min="6" max="6" width="11.81640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.26953125" style="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.26953125" style="1"/>
+    <col min="9" max="11" width="10.26953125" style="1"/>
+    <col min="12" max="12" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -825,8 +851,11 @@
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -834,10 +863,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -851,8 +880,17 @@
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>0.9</v>
       </c>
@@ -879,8 +917,14 @@
         <f>G3*D3</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -908,7 +952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -936,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>1.1499999999999999</v>
       </c>
@@ -964,7 +1008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>1.2</v>
       </c>
@@ -992,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>1.25</v>
       </c>
@@ -1020,7 +1064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>1.3</v>
       </c>
@@ -1048,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <v>1.35</v>
       </c>
@@ -1076,7 +1120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <v>1.4</v>
       </c>
@@ -1104,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <v>1.45</v>
       </c>
@@ -1132,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <v>1.5</v>
       </c>
@@ -1160,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:12">
       <c r="A14" s="1">
         <v>1.55</v>
       </c>
@@ -1188,7 +1232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:12">
       <c r="A15" s="1">
         <v>1.6</v>
       </c>
@@ -1216,7 +1260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:12">
       <c r="A16" s="1">
         <v>1.7</v>
       </c>
@@ -1867,420 +1911,439 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="17.81640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1">
+    <row r="1" spans="1:10" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>43</v>
       </c>
       <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
-        <v>68</v>
-      </c>
       <c r="F1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+    <row r="2" spans="1:10" ht="15" customHeight="1">
       <c r="A2" t="s">
         <v>48</v>
       </c>
       <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2">
+        <v>0.9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" customHeight="1">
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
         <v>51</v>
       </c>
-      <c r="E2">
-        <v>0.9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3">
         <v>-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1">
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:10" ht="15" customHeight="1">
+      <c r="D4" t="s">
         <v>55</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
         <v>56</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4">
         <v>-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1">
-      <c r="C4" t="s">
+    <row r="5" spans="1:10" ht="15" customHeight="1">
+      <c r="D5" t="s">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
         <v>58</v>
       </c>
-      <c r="E4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
+      <c r="G5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5">
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1">
-      <c r="C5" t="s">
+    <row r="6" spans="1:10" ht="15" customHeight="1">
+      <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E6" t="s">
         <v>60</v>
       </c>
-      <c r="E5">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G6">
+        <v>1.2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1">
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7">
+        <v>1.25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1">
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8">
+        <v>1.3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1">
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9">
+        <v>1.35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1">
+      <c r="G10">
+        <v>1.4</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1">
+      <c r="G11">
+        <v>1.45</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1">
+      <c r="G12">
+        <v>1.5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1">
+      <c r="G13">
+        <v>1.55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1">
+      <c r="G14">
+        <v>1.6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1">
+      <c r="G15">
+        <v>1.7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1">
+      <c r="G16">
+        <v>1.8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9" ht="15" customHeight="1">
+      <c r="G17">
+        <v>1.9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="7:9" ht="15" customHeight="1">
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="7:9" ht="15" customHeight="1">
+      <c r="G19">
+        <v>2.1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" ht="15" customHeight="1">
+      <c r="G20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="7:9" ht="15" customHeight="1">
+      <c r="G21">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="7:9" ht="15" customHeight="1">
+      <c r="G22">
+        <v>2.4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="7:9" ht="15" customHeight="1">
+      <c r="G23">
+        <v>2.5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="7:9" ht="15" customHeight="1">
+      <c r="G24">
+        <v>2.6</v>
+      </c>
+      <c r="H24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="7:9" ht="15" customHeight="1">
+      <c r="G25">
+        <v>2.7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25">
         <v>11</v>
       </c>
-      <c r="G5">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1">
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6">
-        <v>1.2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1">
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7">
-        <v>1.25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1">
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8">
-        <v>1.3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1">
-      <c r="D9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9">
-        <v>1.35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1">
-      <c r="E10">
-        <v>1.4</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1">
-      <c r="E11">
-        <v>1.45</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1">
-      <c r="E12">
-        <v>1.5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1">
-      <c r="E13">
-        <v>1.55</v>
-      </c>
-      <c r="F13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1">
-      <c r="E14">
-        <v>1.6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1">
-      <c r="E15">
-        <v>1.7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1">
-      <c r="E16">
-        <v>1.8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="5:7" ht="15" customHeight="1">
-      <c r="E17">
-        <v>1.9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="5:7" ht="15" customHeight="1">
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="5:7" ht="15" customHeight="1">
-      <c r="E19">
-        <v>2.1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="5:7" ht="15" customHeight="1">
-      <c r="E20">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="5:7" ht="15" customHeight="1">
-      <c r="E21">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F21" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="5:7" ht="15" customHeight="1">
-      <c r="E22">
-        <v>2.4</v>
-      </c>
-      <c r="F22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="5:7" ht="15" customHeight="1">
-      <c r="E23">
-        <v>2.5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="5:7" ht="15" customHeight="1">
-      <c r="E24">
-        <v>2.6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="5:7" ht="15" customHeight="1">
-      <c r="E25">
-        <v>2.7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25">
+    </row>
+    <row r="26" spans="7:9" ht="15" customHeight="1">
+      <c r="G26">
+        <v>2.8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="5:7" ht="15" customHeight="1">
-      <c r="E26">
-        <v>2.8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26">
+    <row r="27" spans="7:9" ht="15" customHeight="1">
+      <c r="G27">
+        <v>2.9</v>
+      </c>
+      <c r="H27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="5:7" ht="15" customHeight="1">
-      <c r="E27">
-        <v>2.9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27">
+    <row r="28" spans="7:9" ht="15" customHeight="1">
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="5:7" ht="15" customHeight="1">
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28">
+    <row r="29" spans="7:9" ht="15" customHeight="1">
+      <c r="G29">
+        <v>3.1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="5:7" ht="15" customHeight="1">
-      <c r="E29">
-        <v>3.1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29">
+    <row r="30" spans="7:9" ht="15" customHeight="1">
+      <c r="G30">
+        <v>3.2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="5:7" ht="15" customHeight="1">
-      <c r="E30">
-        <v>3.2</v>
-      </c>
-      <c r="F30" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="5:7" ht="15" customHeight="1">
-      <c r="E31">
+    <row r="31" spans="7:9" ht="15" customHeight="1">
+      <c r="G31">
         <v>3.3</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
         <v>37</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>14</v>
       </c>
     </row>
